--- a/diseases/d019/2010-2014.xlsx
+++ b/diseases/d019/2010-2014.xlsx
@@ -21882,7 +21882,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -22284,7 +22284,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -23680,7 +23680,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -24484,7 +24484,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -24886,7 +24886,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -25880,7 +25880,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -26282,7 +26282,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -27086,7 +27086,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -28080,7 +28080,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -28482,7 +28482,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -29286,7 +29286,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -29688,7 +29688,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -31078,7 +31078,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -31882,7 +31882,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -33278,7 +33278,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34082,7 +34082,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -34484,7 +34484,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -35478,7 +35478,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -35880,7 +35880,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -36282,7 +36282,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -36684,7 +36684,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -37086,7 +37086,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -38080,7 +38080,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -38482,7 +38482,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -38884,7 +38884,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -39286,7 +39286,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -40428,7 +40428,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -40830,7 +40830,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -41232,7 +41232,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -41634,7 +41634,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -42628,7 +42628,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -43030,7 +43030,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -43432,7 +43432,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -43834,7 +43834,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -44236,7 +44236,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -47430,7 +47430,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -47832,7 +47832,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -48234,7 +48234,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -48636,7 +48636,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -49482,7 +49482,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -50032,7 +50032,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -50434,7 +50434,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -50836,7 +50836,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -51238,7 +51238,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -52232,7 +52232,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -52634,7 +52634,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -53036,7 +53036,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -53438,7 +53438,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -54432,7 +54432,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -54834,7 +54834,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -55236,7 +55236,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -55638,7 +55638,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -56484,7 +56484,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -57034,7 +57034,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -57436,7 +57436,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -57838,7 +57838,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -58240,7 +58240,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -59630,7 +59630,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -60032,7 +60032,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -60434,7 +60434,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -60836,7 +60836,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -61830,7 +61830,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -62232,7 +62232,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -62634,7 +62634,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -63036,7 +63036,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -64030,7 +64030,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -64432,7 +64432,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -64834,7 +64834,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -65236,7 +65236,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -65638,7 +65638,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -66632,7 +66632,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -67034,7 +67034,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -67436,7 +67436,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -67838,7 +67838,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -68832,7 +68832,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -69234,7 +69234,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -69636,7 +69636,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -70038,7 +70038,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -70884,7 +70884,7 @@
       </c>
       <c r="AJ408" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK408" t="inlineStr">
@@ -71434,7 +71434,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -71836,7 +71836,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -72238,7 +72238,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -72640,7 +72640,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -73634,7 +73634,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -74036,7 +74036,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -74438,7 +74438,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -74840,7 +74840,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -75834,7 +75834,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -76236,7 +76236,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -76638,7 +76638,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
@@ -77040,7 +77040,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -77442,7 +77442,7 @@
       </c>
       <c r="AJ443" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK443" t="inlineStr">
@@ -78436,7 +78436,7 @@
       </c>
       <c r="AJ449" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK449" t="inlineStr">
@@ -78838,7 +78838,7 @@
       </c>
       <c r="AJ451" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK451" t="inlineStr">
@@ -79240,7 +79240,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -79642,7 +79642,7 @@
       </c>
       <c r="AJ455" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK455" t="inlineStr">
@@ -80636,7 +80636,7 @@
       </c>
       <c r="AJ461" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK461" t="inlineStr">
@@ -81038,7 +81038,7 @@
       </c>
       <c r="AJ463" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK463" t="inlineStr">
@@ -81440,7 +81440,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -81842,7 +81842,7 @@
       </c>
       <c r="AJ467" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK467" t="inlineStr">
@@ -82836,7 +82836,7 @@
       </c>
       <c r="AJ473" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK473" t="inlineStr">
@@ -83238,7 +83238,7 @@
       </c>
       <c r="AJ475" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK475" t="inlineStr">
@@ -83640,7 +83640,7 @@
       </c>
       <c r="AJ477" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK477" t="inlineStr">
@@ -84042,7 +84042,7 @@
       </c>
       <c r="AJ479" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK479" t="inlineStr">
@@ -84444,7 +84444,7 @@
       </c>
       <c r="AJ481" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK481" t="inlineStr">
@@ -85438,7 +85438,7 @@
       </c>
       <c r="AJ487" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK487" t="inlineStr">
@@ -85840,7 +85840,7 @@
       </c>
       <c r="AJ489" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK489" t="inlineStr">
@@ -86242,7 +86242,7 @@
       </c>
       <c r="AJ491" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK491" t="inlineStr">
@@ -86644,7 +86644,7 @@
       </c>
       <c r="AJ493" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK493" t="inlineStr">

--- a/diseases/d019/2010-2014.xlsx
+++ b/diseases/d019/2010-2014.xlsx
@@ -21882,7 +21882,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -22284,7 +22284,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -23680,7 +23680,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -24484,7 +24484,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -24886,7 +24886,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -25880,7 +25880,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -26282,7 +26282,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -27086,7 +27086,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -28080,7 +28080,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -28482,7 +28482,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -29286,7 +29286,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -29688,7 +29688,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -31078,7 +31078,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -31882,7 +31882,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -33278,7 +33278,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34082,7 +34082,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -34484,7 +34484,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -35478,7 +35478,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -35880,7 +35880,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -36282,7 +36282,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -36684,7 +36684,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -37086,7 +37086,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -38080,7 +38080,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -38482,7 +38482,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -38884,7 +38884,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -39286,7 +39286,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -40428,7 +40428,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -40830,7 +40830,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -41232,7 +41232,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -41634,7 +41634,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -42628,7 +42628,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -43030,7 +43030,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -43432,7 +43432,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -43834,7 +43834,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -44236,7 +44236,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -47430,7 +47430,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -47832,7 +47832,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -48234,7 +48234,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -48636,7 +48636,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -49482,7 +49482,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -50032,7 +50032,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -50434,7 +50434,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -50836,7 +50836,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -51238,7 +51238,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -52232,7 +52232,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -52634,7 +52634,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -53036,7 +53036,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -53438,7 +53438,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -54432,7 +54432,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -54834,7 +54834,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -55236,7 +55236,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -55638,7 +55638,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -56484,7 +56484,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -57034,7 +57034,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -57436,7 +57436,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -57838,7 +57838,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -58240,7 +58240,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -59630,7 +59630,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -60032,7 +60032,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -60434,7 +60434,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -60836,7 +60836,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -61830,7 +61830,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -62232,7 +62232,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -62634,7 +62634,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -63036,7 +63036,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -64030,7 +64030,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -64432,7 +64432,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -64834,7 +64834,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -65236,7 +65236,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -65638,7 +65638,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -66632,7 +66632,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -67034,7 +67034,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -67436,7 +67436,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -67838,7 +67838,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -68832,7 +68832,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -69234,7 +69234,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -69636,7 +69636,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -70038,7 +70038,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -70884,7 +70884,7 @@
       </c>
       <c r="AJ408" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK408" t="inlineStr">
@@ -71434,7 +71434,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -71836,7 +71836,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -72238,7 +72238,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -72640,7 +72640,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -73634,7 +73634,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -74036,7 +74036,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -74438,7 +74438,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -74840,7 +74840,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -75834,7 +75834,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -76236,7 +76236,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -76638,7 +76638,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
@@ -77040,7 +77040,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -77442,7 +77442,7 @@
       </c>
       <c r="AJ443" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK443" t="inlineStr">
@@ -78436,7 +78436,7 @@
       </c>
       <c r="AJ449" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK449" t="inlineStr">
@@ -78838,7 +78838,7 @@
       </c>
       <c r="AJ451" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK451" t="inlineStr">
@@ -79240,7 +79240,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -79642,7 +79642,7 @@
       </c>
       <c r="AJ455" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK455" t="inlineStr">
@@ -80636,7 +80636,7 @@
       </c>
       <c r="AJ461" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK461" t="inlineStr">
@@ -81038,7 +81038,7 @@
       </c>
       <c r="AJ463" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK463" t="inlineStr">
@@ -81440,7 +81440,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -81842,7 +81842,7 @@
       </c>
       <c r="AJ467" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK467" t="inlineStr">
@@ -82836,7 +82836,7 @@
       </c>
       <c r="AJ473" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK473" t="inlineStr">
@@ -83238,7 +83238,7 @@
       </c>
       <c r="AJ475" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK475" t="inlineStr">
@@ -83640,7 +83640,7 @@
       </c>
       <c r="AJ477" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK477" t="inlineStr">
@@ -84042,7 +84042,7 @@
       </c>
       <c r="AJ479" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK479" t="inlineStr">
@@ -84444,7 +84444,7 @@
       </c>
       <c r="AJ481" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK481" t="inlineStr">
@@ -85438,7 +85438,7 @@
       </c>
       <c r="AJ487" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK487" t="inlineStr">
@@ -85840,7 +85840,7 @@
       </c>
       <c r="AJ489" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK489" t="inlineStr">
@@ -86242,7 +86242,7 @@
       </c>
       <c r="AJ491" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK491" t="inlineStr">
@@ -86644,7 +86644,7 @@
       </c>
       <c r="AJ493" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK493" t="inlineStr">

--- a/diseases/d019/2010-2014.xlsx
+++ b/diseases/d019/2010-2014.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2197,9 +2191,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2780,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3381,9 +3369,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3973,9 +3958,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4547,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5157,9 +5136,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5749,9 +5725,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6341,9 +6314,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6933,9 +6903,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7525,9 +7492,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8117,9 +8081,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8709,9 +8670,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9105,9 +9063,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9697,9 +9652,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10289,9 +10241,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10881,9 +10830,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11473,9 +11419,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -12065,9 +12008,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12657,9 +12597,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13249,9 +13186,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13841,9 +13775,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14433,9 +14364,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -15025,9 +14953,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15617,9 +15542,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -16209,9 +16131,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16605,9 +16524,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -17197,9 +17113,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -17789,9 +17702,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18381,9 +18291,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -18973,9 +18880,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19565,9 +19469,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -20157,9 +20058,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -20897,9 +20795,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -21489,9 +21384,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -21892,7 +21784,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -22294,7 +22186,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -22696,7 +22588,7 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -23287,9 +23179,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -23690,7 +23579,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -24092,7 +23981,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -24494,7 +24383,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -24896,7 +24785,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -25487,9 +25376,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -25890,7 +25776,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -26292,7 +26178,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -26694,7 +26580,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -27096,7 +26982,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -27687,9 +27573,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -28090,7 +27973,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -28492,7 +28375,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -28894,7 +28777,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -29296,7 +29179,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -29698,7 +29581,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -30289,9 +30172,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -30685,9 +30565,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -31088,7 +30965,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -31490,7 +31367,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -31892,7 +31769,7 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -32294,7 +32171,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -32885,9 +32762,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -33288,7 +33162,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -33690,7 +33564,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -34092,7 +33966,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -34494,7 +34368,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -35085,9 +34959,6 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
@@ -35488,7 +35359,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -35890,7 +35761,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -36292,7 +36163,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -36694,7 +36565,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -37096,7 +36967,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -37687,9 +37558,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -38090,7 +37958,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -38492,7 +38360,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -38894,7 +38762,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -39296,7 +39164,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -39887,9 +39755,6 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -40438,7 +40303,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -40840,7 +40705,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -41242,7 +41107,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -41644,7 +41509,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -42235,9 +42100,6 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0</v>
       </c>
@@ -42638,7 +42500,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -43040,7 +42902,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -43442,7 +43304,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -43844,7 +43706,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -44246,7 +44108,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -44837,9 +44699,6 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0</v>
       </c>
@@ -45240,7 +45099,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -45642,7 +45501,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -46044,7 +45903,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -46446,7 +46305,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -47037,9 +46896,6 @@
       <c r="O279" t="n">
         <v>0</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0</v>
       </c>
@@ -47440,7 +47296,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -47842,7 +47698,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -48244,7 +48100,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -48646,7 +48502,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -49492,7 +49348,7 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN292" t="b">
@@ -49639,9 +49495,6 @@
       <c r="O293" t="n">
         <v>0</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0</v>
       </c>
@@ -50042,7 +49895,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -50444,7 +50297,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -50846,7 +50699,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -51248,7 +51101,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -51839,9 +51692,6 @@
       <c r="O305" t="n">
         <v>0</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0</v>
       </c>
@@ -52242,7 +52092,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -52644,7 +52494,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -53046,7 +52896,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -53448,7 +53298,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -54039,9 +53889,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -54442,7 +54289,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -54844,7 +54691,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -55246,7 +55093,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN323" t="b">
@@ -55648,7 +55495,7 @@
       </c>
       <c r="AM325" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN325" t="b">
@@ -56494,7 +56341,7 @@
       </c>
       <c r="AM330" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN330" t="b">
@@ -56641,9 +56488,6 @@
       <c r="O331" t="n">
         <v>0</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0</v>
       </c>
@@ -57044,7 +56888,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN333" t="b">
@@ -57446,7 +57290,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN335" t="b">
@@ -57848,7 +57692,7 @@
       </c>
       <c r="AM337" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN337" t="b">
@@ -58250,7 +58094,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -58841,9 +58685,6 @@
       <c r="O343" t="n">
         <v>0</v>
       </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
       <c r="R343" t="n">
         <v>0</v>
       </c>
@@ -59237,9 +59078,6 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
@@ -59640,7 +59478,7 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN347" t="b">
@@ -60042,7 +59880,7 @@
       </c>
       <c r="AM349" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN349" t="b">
@@ -60444,7 +60282,7 @@
       </c>
       <c r="AM351" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN351" t="b">
@@ -60846,7 +60684,7 @@
       </c>
       <c r="AM353" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN353" t="b">
@@ -61437,9 +61275,6 @@
       <c r="O357" t="n">
         <v>0</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0</v>
       </c>
@@ -61840,7 +61675,7 @@
       </c>
       <c r="AM359" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN359" t="b">
@@ -62242,7 +62077,7 @@
       </c>
       <c r="AM361" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN361" t="b">
@@ -62644,7 +62479,7 @@
       </c>
       <c r="AM363" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN363" t="b">
@@ -63046,7 +62881,7 @@
       </c>
       <c r="AM365" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN365" t="b">
@@ -63637,9 +63472,6 @@
       <c r="O369" t="n">
         <v>0</v>
       </c>
-      <c r="Q369" t="n">
-        <v>0</v>
-      </c>
       <c r="R369" t="n">
         <v>0</v>
       </c>
@@ -64040,7 +63872,7 @@
       </c>
       <c r="AM371" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN371" t="b">
@@ -64442,7 +64274,7 @@
       </c>
       <c r="AM373" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN373" t="b">
@@ -64844,7 +64676,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -65246,7 +65078,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN377" t="b">
@@ -65648,7 +65480,7 @@
       </c>
       <c r="AM379" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN379" t="b">
@@ -66239,9 +66071,6 @@
       <c r="O383" t="n">
         <v>0</v>
       </c>
-      <c r="Q383" t="n">
-        <v>0</v>
-      </c>
       <c r="R383" t="n">
         <v>0</v>
       </c>
@@ -66642,7 +66471,7 @@
       </c>
       <c r="AM385" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN385" t="b">
@@ -67044,7 +66873,7 @@
       </c>
       <c r="AM387" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN387" t="b">
@@ -67446,7 +67275,7 @@
       </c>
       <c r="AM389" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN389" t="b">
@@ -67848,7 +67677,7 @@
       </c>
       <c r="AM391" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN391" t="b">
@@ -68439,9 +68268,6 @@
       <c r="O395" t="n">
         <v>0</v>
       </c>
-      <c r="Q395" t="n">
-        <v>0</v>
-      </c>
       <c r="R395" t="n">
         <v>0</v>
       </c>
@@ -68842,7 +68668,7 @@
       </c>
       <c r="AM397" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN397" t="b">
@@ -69244,7 +69070,7 @@
       </c>
       <c r="AM399" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN399" t="b">
@@ -69646,7 +69472,7 @@
       </c>
       <c r="AM401" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN401" t="b">
@@ -70048,7 +69874,7 @@
       </c>
       <c r="AM403" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN403" t="b">
@@ -70894,7 +70720,7 @@
       </c>
       <c r="AM408" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN408" t="b">
@@ -71041,9 +70867,6 @@
       <c r="O409" t="n">
         <v>0</v>
       </c>
-      <c r="Q409" t="n">
-        <v>0</v>
-      </c>
       <c r="R409" t="n">
         <v>0</v>
       </c>
@@ -71444,7 +71267,7 @@
       </c>
       <c r="AM411" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN411" t="b">
@@ -71846,7 +71669,7 @@
       </c>
       <c r="AM413" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN413" t="b">
@@ -72248,7 +72071,7 @@
       </c>
       <c r="AM415" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN415" t="b">
@@ -72650,7 +72473,7 @@
       </c>
       <c r="AM417" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN417" t="b">
@@ -73241,9 +73064,6 @@
       <c r="O421" t="n">
         <v>0</v>
       </c>
-      <c r="Q421" t="n">
-        <v>0</v>
-      </c>
       <c r="R421" t="n">
         <v>0</v>
       </c>
@@ -73644,7 +73464,7 @@
       </c>
       <c r="AM423" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN423" t="b">
@@ -74046,7 +73866,7 @@
       </c>
       <c r="AM425" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN425" t="b">
@@ -74448,7 +74268,7 @@
       </c>
       <c r="AM427" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN427" t="b">
@@ -74850,7 +74670,7 @@
       </c>
       <c r="AM429" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN429" t="b">
@@ -75441,9 +75261,6 @@
       <c r="O433" t="n">
         <v>0</v>
       </c>
-      <c r="Q433" t="n">
-        <v>0</v>
-      </c>
       <c r="R433" t="n">
         <v>0</v>
       </c>
@@ -75844,7 +75661,7 @@
       </c>
       <c r="AM435" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN435" t="b">
@@ -76246,7 +76063,7 @@
       </c>
       <c r="AM437" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN437" t="b">
@@ -76648,7 +76465,7 @@
       </c>
       <c r="AM439" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN439" t="b">
@@ -77050,7 +76867,7 @@
       </c>
       <c r="AM441" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN441" t="b">
@@ -77452,7 +77269,7 @@
       </c>
       <c r="AM443" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN443" t="b">
@@ -78043,9 +77860,6 @@
       <c r="O447" t="n">
         <v>0</v>
       </c>
-      <c r="Q447" t="n">
-        <v>0</v>
-      </c>
       <c r="R447" t="n">
         <v>0</v>
       </c>
@@ -78446,7 +78260,7 @@
       </c>
       <c r="AM449" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN449" t="b">
@@ -78848,7 +78662,7 @@
       </c>
       <c r="AM451" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN451" t="b">
@@ -79250,7 +79064,7 @@
       </c>
       <c r="AM453" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN453" t="b">
@@ -79652,7 +79466,7 @@
       </c>
       <c r="AM455" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN455" t="b">
@@ -80243,9 +80057,6 @@
       <c r="O459" t="n">
         <v>0</v>
       </c>
-      <c r="Q459" t="n">
-        <v>0</v>
-      </c>
       <c r="R459" t="n">
         <v>0</v>
       </c>
@@ -80646,7 +80457,7 @@
       </c>
       <c r="AM461" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN461" t="b">
@@ -81048,7 +80859,7 @@
       </c>
       <c r="AM463" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN463" t="b">
@@ -81450,7 +81261,7 @@
       </c>
       <c r="AM465" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN465" t="b">
@@ -81852,7 +81663,7 @@
       </c>
       <c r="AM467" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN467" t="b">
@@ -82443,9 +82254,6 @@
       <c r="O471" t="n">
         <v>0</v>
       </c>
-      <c r="Q471" t="n">
-        <v>0</v>
-      </c>
       <c r="R471" t="n">
         <v>0</v>
       </c>
@@ -82846,7 +82654,7 @@
       </c>
       <c r="AM473" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN473" t="b">
@@ -83248,7 +83056,7 @@
       </c>
       <c r="AM475" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN475" t="b">
@@ -83650,7 +83458,7 @@
       </c>
       <c r="AM477" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN477" t="b">
@@ -84052,7 +83860,7 @@
       </c>
       <c r="AM479" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN479" t="b">
@@ -84454,7 +84262,7 @@
       </c>
       <c r="AM481" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN481" t="b">
@@ -85045,9 +84853,6 @@
       <c r="O485" t="n">
         <v>0</v>
       </c>
-      <c r="Q485" t="n">
-        <v>0</v>
-      </c>
       <c r="R485" t="n">
         <v>0</v>
       </c>
@@ -85448,7 +85253,7 @@
       </c>
       <c r="AM487" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN487" t="b">
@@ -85850,7 +85655,7 @@
       </c>
       <c r="AM489" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN489" t="b">
@@ -86252,7 +86057,7 @@
       </c>
       <c r="AM491" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN491" t="b">
@@ -86654,7 +86459,7 @@
       </c>
       <c r="AM493" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN493" t="b">

--- a/diseases/d019/2010-2014.xlsx
+++ b/diseases/d019/2010-2014.xlsx
@@ -21774,7 +21774,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -23569,7 +23569,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -23971,7 +23971,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -24373,7 +24373,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -26168,7 +26168,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -26570,7 +26570,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -26972,7 +26972,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -27963,7 +27963,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -28767,7 +28767,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -29169,7 +29169,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -29571,7 +29571,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -30955,7 +30955,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -31357,7 +31357,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -31759,7 +31759,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -32161,7 +32161,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -33152,7 +33152,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -33554,7 +33554,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -33956,7 +33956,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -34358,7 +34358,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -35349,7 +35349,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -35751,7 +35751,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -36153,7 +36153,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -36555,7 +36555,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -36957,7 +36957,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37948,7 +37948,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -38350,7 +38350,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -38752,7 +38752,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -39154,7 +39154,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -40293,7 +40293,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -40695,7 +40695,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -41097,7 +41097,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -41499,7 +41499,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -42490,7 +42490,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -42892,7 +42892,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -43294,7 +43294,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -43696,7 +43696,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -44098,7 +44098,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -45089,7 +45089,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -45491,7 +45491,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -45893,7 +45893,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -46295,7 +46295,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -47286,7 +47286,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -47688,7 +47688,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -48090,7 +48090,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -48492,7 +48492,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -49338,7 +49338,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -49885,7 +49885,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -50287,7 +50287,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -50689,7 +50689,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -51091,7 +51091,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -52082,7 +52082,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -52484,7 +52484,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -52886,7 +52886,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -53288,7 +53288,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -54279,7 +54279,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -54681,7 +54681,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -55083,7 +55083,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -55485,7 +55485,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -56331,7 +56331,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -56878,7 +56878,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -57280,7 +57280,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -57682,7 +57682,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -58084,7 +58084,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -59468,7 +59468,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -59870,7 +59870,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -60272,7 +60272,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -60674,7 +60674,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -61665,7 +61665,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -62067,7 +62067,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -62469,7 +62469,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -62871,7 +62871,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -63862,7 +63862,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -64264,7 +64264,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -64666,7 +64666,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -65068,7 +65068,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -65470,7 +65470,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -66461,7 +66461,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -66863,7 +66863,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -67265,7 +67265,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -67667,7 +67667,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -68658,7 +68658,7 @@
       </c>
       <c r="AJ397" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK397" t="inlineStr">
@@ -69060,7 +69060,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -69462,7 +69462,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -69864,7 +69864,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -70710,7 +70710,7 @@
       </c>
       <c r="AJ408" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK408" t="inlineStr">
@@ -71257,7 +71257,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -71659,7 +71659,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -72061,7 +72061,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -72463,7 +72463,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -73454,7 +73454,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -73856,7 +73856,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -74258,7 +74258,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -74660,7 +74660,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -75651,7 +75651,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -76053,7 +76053,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -76455,7 +76455,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
@@ -76857,7 +76857,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -77259,7 +77259,7 @@
       </c>
       <c r="AJ443" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK443" t="inlineStr">
@@ -78250,7 +78250,7 @@
       </c>
       <c r="AJ449" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK449" t="inlineStr">
@@ -78652,7 +78652,7 @@
       </c>
       <c r="AJ451" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK451" t="inlineStr">
@@ -79054,7 +79054,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -79456,7 +79456,7 @@
       </c>
       <c r="AJ455" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK455" t="inlineStr">
@@ -80447,7 +80447,7 @@
       </c>
       <c r="AJ461" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK461" t="inlineStr">
@@ -80849,7 +80849,7 @@
       </c>
       <c r="AJ463" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK463" t="inlineStr">
@@ -81251,7 +81251,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -81653,7 +81653,7 @@
       </c>
       <c r="AJ467" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK467" t="inlineStr">
@@ -82644,7 +82644,7 @@
       </c>
       <c r="AJ473" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK473" t="inlineStr">
@@ -83046,7 +83046,7 @@
       </c>
       <c r="AJ475" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK475" t="inlineStr">
@@ -83448,7 +83448,7 @@
       </c>
       <c r="AJ477" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK477" t="inlineStr">
@@ -83850,7 +83850,7 @@
       </c>
       <c r="AJ479" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK479" t="inlineStr">
@@ -84252,7 +84252,7 @@
       </c>
       <c r="AJ481" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK481" t="inlineStr">
@@ -85243,7 +85243,7 @@
       </c>
       <c r="AJ487" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK487" t="inlineStr">
@@ -85645,7 +85645,7 @@
       </c>
       <c r="AJ489" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK489" t="inlineStr">
@@ -86047,7 +86047,7 @@
       </c>
       <c r="AJ491" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK491" t="inlineStr">
@@ -86449,7 +86449,7 @@
       </c>
       <c r="AJ493" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK493" t="inlineStr">
